--- a/Expert Automation Final v02.xlsx
+++ b/Expert Automation Final v02.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qi.qu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA9CB6F-5D97-4C34-8C77-AF79C5E38EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76DABDE-E69C-4727-8625-E82B16B83CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4344" yWindow="1236" windowWidth="17280" windowHeight="8880" xr2:uid="{01915C0D-4F25-4949-B12A-8FD1DC934101}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{01915C0D-4F25-4949-B12A-8FD1DC934101}"/>
   </bookViews>
   <sheets>
     <sheet name="Models" sheetId="1" r:id="rId1"/>
     <sheet name="Combination" sheetId="3" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Models!$A$1:$L$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Models!$A$1:$L$59</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,8 +42,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="103">
   <si>
     <t>Product code</t>
   </si>
@@ -132,9 +157,6 @@
     <t>HCR3818DWMM</t>
   </si>
   <si>
-    <t>HCR59F18DNMB</t>
-  </si>
-  <si>
     <t>CBI Cooling</t>
   </si>
   <si>
@@ -343,6 +365,15 @@
   </si>
   <si>
     <t>Product price</t>
+  </si>
+  <si>
+    <t>HW110-BD14397U1</t>
+  </si>
+  <si>
+    <t>HWD120-BD16397EU1</t>
+  </si>
+  <si>
+    <t>HD90-A3Q397U1</t>
   </si>
 </sst>
 </file>
@@ -648,6 +679,5946 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Washing old"/>
+      <sheetName val="Washing"/>
+      <sheetName val="Energysaving Otto and BF MSH"/>
+      <sheetName val="Cooling old"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="CBI DW"/>
+      <sheetName val="Cooling base. WIP"/>
+      <sheetName val="Cooling"/>
+      <sheetName val="CBI all"/>
+      <sheetName val="NPIs"/>
+      <sheetName val="CBI (all)"/>
+      <sheetName val="Product Feature"/>
+      <sheetName val="Consumables"/>
+      <sheetName val="Tabelle1"/>
+      <sheetName val="Comment"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="EXP_CBI" refersTo="='CBI all'!$Y:$Y"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="Y4" t="str">
+            <v>Motorart/ Motor type</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="Y5" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="Y6" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="Y7" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="Y8" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="Y9" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="Y10" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="Y11" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="Y12" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="Y13" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="Y14" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="Y15" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="Y16" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="Y17" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="Y18" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="Y19" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="Y20" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="Y21" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="Y22" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="Y23" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="Y24" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="Y25" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="Y26" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="Y27" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="Y28" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="Y29" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="Y30" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="Y31" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="Y32" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Y33" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="Y34" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="Y35" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="Y36" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="Y37" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="Y38" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="Y39" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="Y40" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="Y41" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="Y42" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="Y43" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="Y44" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="Y45" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="Y46" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="Y47" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="Y48" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="Y49" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="Y50" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="Y51" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="Y52" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="Y53" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="Y54" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="Y55" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="Y56" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="Y57" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="Y58" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="Y59" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="Y60" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="Y61" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="Y62" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="Y63" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="Y64" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="Y65" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="Y66" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="Y67" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="Y68" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="Y69" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="Y70" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="Y71" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="Y72" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="Y73" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="Y74" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="Y75" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="Y76" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="Y77" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="Y78" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="Y79" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="Y80" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="Y81" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="Y82" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="Y83" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="Y84" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="Y85" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="Y86" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="Y87" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="Y88" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="Y89" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="Y90" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="Y91" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="Y92" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="Y93" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="Y94" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="Y95" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="Y96" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="Y97" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="Y98" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="Y99" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="Y100" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="Y101" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="Y102" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="Y103" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="Y104" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="Y105" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="Y106" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="Y107" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="Y108" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="Y109" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="Y110" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="Y111" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="Y112" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="Y113" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="Y114" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="Y115" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="Y116" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="Y117" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="Y118" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="Y119" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="Y120" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="Y121" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="Y122" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="Y123" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="Y124" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="Y125" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="Y126" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="Y127" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="Y128" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="Y129" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="Y130" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="Y131" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="Y132" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="Y133" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="Y134" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="Y135" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="Y136" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="Y137" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="Y138" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="Y139" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="Y140" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="Y141" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="Y142" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="Y143" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="Y144" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="Y145" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="Y146" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="Y147" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="Y148" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="Y149" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="Y150" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="Y151" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="Y152" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="Y153" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="Y154" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="Y155" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="Y156" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="Y157" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="Y158" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="Y159" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="Y160" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="Y161" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="Y162" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="Y163" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="Y164" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="Y165" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="Y166" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="Y167" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="Y168" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="E1" t="str">
+            <v>Productname</v>
+          </cell>
+          <cell r="Y1" t="str">
+            <v>Motorart/ Motor type</v>
+          </cell>
+          <cell r="DM1" t="str">
+            <v>Expert</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="E2" t="str">
+            <v>HW70-BP14636N</v>
+          </cell>
+          <cell r="Y2" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="E3" t="str">
+            <v>HW80-BP14636N</v>
+          </cell>
+          <cell r="Y3" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="E4" t="str">
+            <v>HW90-BP14636N</v>
+          </cell>
+          <cell r="Y4" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5" t="str">
+            <v>HW100-BP14636N</v>
+          </cell>
+          <cell r="Y5" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="E6" t="str">
+            <v>HW70-BP14929BU1</v>
+          </cell>
+          <cell r="Y6" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="E7" t="str">
+            <v>HW70-BP14929</v>
+          </cell>
+          <cell r="Y7" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="E8" t="str">
+            <v>HW80-BP14929BU1</v>
+          </cell>
+          <cell r="Y8" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="E9" t="str">
+            <v>HW80-BP14929</v>
+          </cell>
+          <cell r="Y9" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="E10" t="str">
+            <v>HW90-BP14929BU1</v>
+          </cell>
+          <cell r="Y10" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="E11" t="str">
+            <v>HW90-BP14929</v>
+          </cell>
+          <cell r="Y11" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="E12" t="str">
+            <v>HW100-BP14929</v>
+          </cell>
+          <cell r="Y12" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="E13" t="str">
+            <v>HW70-B14929</v>
+          </cell>
+          <cell r="Y13" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="E14" t="str">
+            <v>HW80-B14939W</v>
+          </cell>
+          <cell r="Y14" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="E15" t="str">
+            <v>HW80-B14939</v>
+          </cell>
+          <cell r="Y15" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="E16" t="str">
+            <v>HW90-BP14939</v>
+          </cell>
+          <cell r="Y16" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="E17" t="str">
+            <v>HW90-B14939</v>
+          </cell>
+          <cell r="Y17" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18" t="str">
+            <v>HW100-B14939</v>
+          </cell>
+          <cell r="Y18" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v>HW81-NBP14939</v>
+          </cell>
+          <cell r="Y19" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="E20" t="str">
+            <v>HW91-NBP14939</v>
+          </cell>
+          <cell r="Y20" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>HW101-NBP14939</v>
+          </cell>
+          <cell r="Y21" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="E22" t="str">
+            <v>HW80-B14959EU1</v>
+          </cell>
+          <cell r="Y22" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="E23" t="str">
+            <v>HW80-B14959YEU1</v>
+          </cell>
+          <cell r="Y23" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="E24" t="str">
+            <v>HW90-B14959U1</v>
+          </cell>
+          <cell r="Y24" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="E25" t="str">
+            <v>HW90-B14959EU1</v>
+          </cell>
+          <cell r="Y25" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="E26" t="str">
+            <v>HW100-B14959U1</v>
+          </cell>
+          <cell r="Y26" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="E27" t="str">
+            <v>HW80-B14979</v>
+          </cell>
+          <cell r="Y27" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="E28" t="str">
+            <v>HW90-B14979</v>
+          </cell>
+          <cell r="Y28" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="E29" t="str">
+            <v>HW80-BD14979EU1</v>
+          </cell>
+          <cell r="Y29" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="E30" t="str">
+            <v>HW90-BD14979U1</v>
+          </cell>
+          <cell r="Y30" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="E31" t="str">
+            <v>HW90-BD14979EU1</v>
+          </cell>
+          <cell r="Y31" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="E32" t="str">
+            <v>HW90-B14979YU1</v>
+          </cell>
+          <cell r="Y32" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="E33" t="str">
+            <v>HW100-BD14979U1</v>
+          </cell>
+          <cell r="Y33" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="E34" t="str">
+            <v>HW110-B14979U1</v>
+          </cell>
+          <cell r="Y34" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="E35" t="str">
+            <v>HW120-B14979EU1</v>
+          </cell>
+          <cell r="Y35" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="E36" t="str">
+            <v>HW50-BP12307</v>
+          </cell>
+          <cell r="Y36" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="E37" t="str">
+            <v>HW50-BP12307U1</v>
+          </cell>
+          <cell r="Y37" t="str">
+            <v>BLDC</v>
+          </cell>
+          <cell r="DM37">
+            <v>379</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="E38" t="str">
+            <v>HW50-BP12307AU1</v>
+          </cell>
+          <cell r="Y38" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="E39" t="str">
+            <v>HW50-BP12307GU1</v>
+          </cell>
+          <cell r="Y39" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="E40" t="str">
+            <v>HW90-B145X-LINE</v>
+          </cell>
+          <cell r="Y40" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="E41" t="str">
+            <v>HW90-B14TEAM5</v>
+          </cell>
+          <cell r="Y41" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="E42" t="str">
+            <v>HW100-BD14397U1</v>
+          </cell>
+          <cell r="Y42" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="E43" t="str">
+            <v>HW110-BD14397U1</v>
+          </cell>
+          <cell r="Y43" t="str">
+            <v>DD</v>
+          </cell>
+          <cell r="DM43">
+            <v>545</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="E44" t="str">
+            <v>HW100-BP14357U1</v>
+          </cell>
+          <cell r="Y44" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="E45" t="str">
+            <v>HW110-BP14357U1</v>
+          </cell>
+          <cell r="Y45" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="E46" t="str">
+            <v>HWD100-BP14939</v>
+          </cell>
+          <cell r="Y46" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="E47" t="str">
+            <v>HWD100-B14939</v>
+          </cell>
+          <cell r="Y47" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="E48" t="str">
+            <v>HWD80-B14939</v>
+          </cell>
+          <cell r="Y48" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="E49" t="str">
+            <v>HWD90-B14959U1</v>
+          </cell>
+          <cell r="Y49" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="E50" t="str">
+            <v>HWD80-B14979</v>
+          </cell>
+          <cell r="Y50" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="E51" t="str">
+            <v>HWD100-BD14979U1</v>
+          </cell>
+          <cell r="Y51" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="E52" t="str">
+            <v>HWD120-B14979U1</v>
+          </cell>
+          <cell r="Y52" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="E53" t="str">
+            <v>HWD80-B14979U1</v>
+          </cell>
+          <cell r="Y53" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="E54" t="str">
+            <v>HWD100-BD14397U1​</v>
+          </cell>
+          <cell r="Y54" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="E55" t="str">
+            <v>HWD120-BD16397EU1</v>
+          </cell>
+          <cell r="Y55" t="str">
+            <v>DD</v>
+          </cell>
+          <cell r="DM55">
+            <v>1050</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="E56" t="str">
+            <v>HWD120-BP14357U1</v>
+          </cell>
+          <cell r="Y56" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="E57" t="str">
+            <v>HWD50-BP12307U1</v>
+          </cell>
+          <cell r="Y57" t="str">
+            <v>BLDC</v>
+          </cell>
+          <cell r="DM57">
+            <v>499</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="E58" t="str">
+            <v>RTXSGQ47TMC5/-84</v>
+          </cell>
+          <cell r="Y58" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="E59" t="str">
+            <v>RTXSGP47TMSCE-84</v>
+          </cell>
+          <cell r="Y59" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="E60" t="str">
+            <v>RTXSGQ48TMSCE-84</v>
+          </cell>
+          <cell r="Y60" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="E61" t="str">
+            <v>THASNQ466TM4-84</v>
+          </cell>
+          <cell r="Y61" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="E62" t="str">
+            <v>THASNQ476TM5-84</v>
+          </cell>
+          <cell r="Y62" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="E63" t="str">
+            <v>THASNQ476TM4-84</v>
+          </cell>
+          <cell r="Y63" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="E64" t="str">
+            <v>THASNQ286TMR5-84</v>
+          </cell>
+          <cell r="Y64" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="E65" t="str">
+            <v>THASNQ286TM5-84</v>
+          </cell>
+          <cell r="Y65" t="str">
+            <v>BLDC</v>
+          </cell>
+          <cell r="DM65">
+            <v>299</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="E66" t="str">
+            <v>HD80-E929E</v>
+          </cell>
+          <cell r="Y66" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="E67" t="str">
+            <v>HD81-A3939E</v>
+          </cell>
+          <cell r="Y67" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="E68" t="str">
+            <v>HD80-A2939</v>
+          </cell>
+          <cell r="Y68" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="E69" t="str">
+            <v>HD91-A3939E</v>
+          </cell>
+          <cell r="Y69" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="E70" t="str">
+            <v>HD90-A2939</v>
+          </cell>
+          <cell r="Y70" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="E71" t="str">
+            <v>HD81-A3959E</v>
+          </cell>
+          <cell r="Y71" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="E72" t="str">
+            <v>HD80-A3959</v>
+          </cell>
+          <cell r="Y72" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="E73" t="str">
+            <v>HD91-A3959E</v>
+          </cell>
+          <cell r="Y73" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="E74" t="str">
+            <v>HD90-A3959</v>
+          </cell>
+          <cell r="Y74" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="E75" t="str">
+            <v>HD100-A2979N</v>
+          </cell>
+          <cell r="Y75" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="E76" t="str">
+            <v>HD90-A3Q979U1</v>
+          </cell>
+          <cell r="Y76" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="E77" t="str">
+            <v>HD90-A35XLINE-DE</v>
+          </cell>
+          <cell r="Y77" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="E78" t="str">
+            <v>HD90-A3TEAM5</v>
+          </cell>
+          <cell r="Y78" t="str">
+            <v>BLDC</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="E79" t="str">
+            <v>HD90-A3Q397U1</v>
+          </cell>
+          <cell r="Y79" t="str">
+            <v>BLDC</v>
+          </cell>
+          <cell r="DM79">
+            <v>629</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="E80" t="str">
+            <v>H3W4 272DA3/1-S</v>
+          </cell>
+          <cell r="Y80" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="E81" t="str">
+            <v>H3W 482DA3/1-S</v>
+          </cell>
+          <cell r="Y81" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="E82" t="str">
+            <v>H3WOSQ485TA4-84</v>
+          </cell>
+          <cell r="Y82" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="E83" t="str">
+            <v>H3WOSQ495TA4-84</v>
+          </cell>
+          <cell r="Y83" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="E84" t="str">
+            <v>H3WOSQ4105TA4-84</v>
+          </cell>
+          <cell r="Y84" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="E85" t="str">
+            <v>RH3W 48HMCB-84</v>
+          </cell>
+          <cell r="Y85" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="E86" t="str">
+            <v>RH3W 49HMCB-84</v>
+          </cell>
+          <cell r="Y86" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="E87" t="str">
+            <v>HWQ4 47AMC/1-84</v>
+          </cell>
+          <cell r="Y87" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="E88" t="str">
+            <v>HWQ 48AMC/1-84</v>
+          </cell>
+          <cell r="Y88" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="E89" t="str">
+            <v>HWQ 49AMC6/1-84</v>
+          </cell>
+          <cell r="Y89" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="E90" t="str">
+            <v>HWQ 410AMC6/1-84</v>
+          </cell>
+          <cell r="Y90" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="E91" t="str">
+            <v>H7W4 48MBC-84</v>
+          </cell>
+          <cell r="Y91" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="E92" t="str">
+            <v>H7W4 49MBC-84</v>
+          </cell>
+          <cell r="Y92" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="E93" t="str">
+            <v>H7W 4105MBC-84</v>
+          </cell>
+          <cell r="Y93" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="E94" t="str">
+            <v>H7W 412MBC-84</v>
+          </cell>
+          <cell r="Y94" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="E95" t="str">
+            <v>H3TMQ 06TAE/1-84</v>
+          </cell>
+          <cell r="Y95" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="E96" t="str">
+            <v>H3TMQ 47TAE/1-84</v>
+          </cell>
+          <cell r="Y96" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="E97" t="str">
+            <v>H3TSMQ47TAMCE-84</v>
+          </cell>
+          <cell r="Y97" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="E98" t="str">
+            <v>H3TMQ285TAMCE84</v>
+          </cell>
+          <cell r="Y98" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="E99" t="str">
+            <v>H3TSMQ48TAMCE-84</v>
+          </cell>
+          <cell r="Y99" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="E100" t="str">
+            <v>THOSQ275D3-S</v>
+          </cell>
+          <cell r="Y100" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="E101" t="str">
+            <v>THOQ474TM5-84</v>
+          </cell>
+          <cell r="Y101" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="E102" t="str">
+            <v>THOSQ486TM4-84</v>
+          </cell>
+          <cell r="Y102" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="E103" t="str">
+            <v>THOSQ085D2-S</v>
+          </cell>
+          <cell r="Y103" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="E104" t="str">
+            <v>H3DO4755T2/1-84</v>
+          </cell>
+          <cell r="Y104" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="E105" t="str">
+            <v>HDQ 475AMC-84</v>
+          </cell>
+          <cell r="Y105" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="E106" t="str">
+            <v>HDQ 485AMC-84</v>
+          </cell>
+          <cell r="Y106" t="str">
+            <v>Inverter</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="E107" t="str">
+            <v>HLE C7DE-84</v>
+          </cell>
+          <cell r="Y107" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="E108" t="str">
+            <v>HLE C8DE-84</v>
+          </cell>
+          <cell r="Y108" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="E109" t="str">
+            <v>ND4 H7A2TCE-84</v>
+          </cell>
+          <cell r="Y109" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="E110" t="str">
+            <v>NDE H7A2TCES-84</v>
+          </cell>
+          <cell r="Y110" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="E111" t="str">
+            <v>NDE H8A2TCES-84</v>
+          </cell>
+          <cell r="Y111" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="E112" t="str">
+            <v>NDEH10A2TCBES-84</v>
+          </cell>
+          <cell r="Y112" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="E113" t="str">
+            <v>HW70-BP14637T</v>
+          </cell>
+          <cell r="Y113" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM113">
+            <v>225</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="E114" t="str">
+            <v>HW70-BP1433637T</v>
+          </cell>
+          <cell r="Y114" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="E115" t="str">
+            <v>HW80-BP14637T</v>
+          </cell>
+          <cell r="Y115" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="E116" t="str">
+            <v>HW80-BP1427637T</v>
+          </cell>
+          <cell r="Y116" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="E117" t="str">
+            <v>HW80-BP1426637T</v>
+          </cell>
+          <cell r="Y117" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM117">
+            <v>239</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="E118" t="str">
+            <v>HW80-BP1433637T</v>
+          </cell>
+          <cell r="Y118" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="E119" t="str">
+            <v>HW90-BP14637T</v>
+          </cell>
+          <cell r="Y119" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="E120" t="str">
+            <v>HW90-BP1426637T</v>
+          </cell>
+          <cell r="Y120" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="E121" t="str">
+            <v>HW90-BP1433637T</v>
+          </cell>
+          <cell r="Y121" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="E122" t="str">
+            <v>HW100-BP14637</v>
+          </cell>
+          <cell r="Y122" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM122">
+            <v>289</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="E123" t="str">
+            <v>HW100-BP1427637</v>
+          </cell>
+          <cell r="Y123" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="E124" t="str">
+            <v>HW100-BP1433637</v>
+          </cell>
+          <cell r="Y124" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="E125" t="str">
+            <v>HW70-BP14657TU1</v>
+          </cell>
+          <cell r="Y125" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="E126" t="str">
+            <v>HW80-BP14657TU1</v>
+          </cell>
+          <cell r="Y126" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM126">
+            <v>297</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="E127" t="str">
+            <v>HW80-BP14W657U1</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="E128" t="str">
+            <v>HW90-BP14657TU1</v>
+          </cell>
+          <cell r="Y128" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM128">
+            <v>309</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="E129" t="str">
+            <v>HW90-BP1427657TU1</v>
+          </cell>
+          <cell r="Y129" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="E130" t="str">
+            <v>HW90-BP1433657TU1</v>
+          </cell>
+          <cell r="Y130" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="E131" t="str">
+            <v>HW90-BP14657BTU1</v>
+          </cell>
+          <cell r="Y131" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="E132" t="str">
+            <v>HW90-BP1433657BTU1</v>
+          </cell>
+          <cell r="Y132" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="E133" t="str">
+            <v>HW120-BP14657U1</v>
+          </cell>
+          <cell r="Y133" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="E134" t="str">
+            <v>HW140-BP14657U1</v>
+          </cell>
+          <cell r="Y134" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="E135" t="str">
+            <v>HW80-B14667TU1</v>
+          </cell>
+          <cell r="Y135" t="str">
+            <v>DD</v>
+          </cell>
+          <cell r="DM135">
+            <v>375</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="E136" t="str">
+            <v>HW90-B14667TU1</v>
+          </cell>
+          <cell r="Y136" t="str">
+            <v>DD</v>
+          </cell>
+          <cell r="DM136">
+            <v>399</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="E137" t="str">
+            <v>HW90-B14W667U1</v>
+          </cell>
+          <cell r="Y137" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="E138" t="str">
+            <v>HW100-B14667U1</v>
+          </cell>
+          <cell r="Y138" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="E139" t="str">
+            <v>HW130-B14667U1</v>
+          </cell>
+          <cell r="Y139" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="E140" t="str">
+            <v>HW130-B14687U1</v>
+          </cell>
+          <cell r="Y140" t="str">
+            <v>DD</v>
+          </cell>
+          <cell r="DM140">
+            <v>582</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="E141" t="str">
+            <v>HWD80-BP14637T</v>
+          </cell>
+          <cell r="Y141" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM141">
+            <v>323</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="E142" t="str">
+            <v>HWD80-BP1433637T</v>
+          </cell>
+          <cell r="Y142" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="E143" t="str">
+            <v>HWD100-BP14657U1</v>
+          </cell>
+          <cell r="Y143" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM143">
+            <v>407</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="E144" t="str">
+            <v>HWD130-BP14657U1</v>
+          </cell>
+          <cell r="Y144" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="E145" t="str">
+            <v>HWD90-BP14667TU1</v>
+          </cell>
+          <cell r="Y145" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="E146" t="str">
+            <v>HWD80-BP14687TU1</v>
+          </cell>
+          <cell r="Y146" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="E147" t="str">
+            <v>HW90-BPD13386U1</v>
+          </cell>
+          <cell r="Y147" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="E148" t="str">
+            <v>HW90-BPD13386GU1</v>
+          </cell>
+          <cell r="Y148" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM148">
+            <v>583</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="E149" t="str">
+            <v>HD80-C33637</v>
+          </cell>
+          <cell r="Y149" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="E150" t="str">
+            <v>HD80-D637</v>
+          </cell>
+          <cell r="Y150" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="E151" t="str">
+            <v>HD90-C637</v>
+          </cell>
+          <cell r="Y151" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM151">
+            <v>329</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="E152" t="str">
+            <v>HD80-C657U1</v>
+          </cell>
+          <cell r="Y152" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM152">
+            <v>335</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="E153" t="str">
+            <v>HD90-C657U1</v>
+          </cell>
+          <cell r="Y153" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="E154" t="str">
+            <v>HD90-C33657U1</v>
+          </cell>
+          <cell r="Y154" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="E155" t="str">
+            <v>HD90-C657BU1</v>
+          </cell>
+          <cell r="Y155" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="E156" t="str">
+            <v>HD90-C33657BU1</v>
+          </cell>
+          <cell r="Y156" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="E157" t="str">
+            <v>HD90-B667U1</v>
+          </cell>
+          <cell r="Y157" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM157">
+            <v>428</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="E158" t="str">
+            <v>HD90-B667WU1</v>
+          </cell>
+          <cell r="Y158" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="E159" t="str">
+            <v>HD90-A687U1</v>
+          </cell>
+          <cell r="Y159" t="str">
+            <v>BPM</v>
+          </cell>
+          <cell r="DM159">
+            <v>472</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="E160" t="str">
+            <v>HEYQ27SB7-84</v>
+          </cell>
+          <cell r="Y160" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="E161" t="str">
+            <v>HGDQ48SB6-84</v>
+          </cell>
+          <cell r="Y161" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="E162" t="str">
+            <v>HGDQ49SBL8U-84</v>
+          </cell>
+          <cell r="Y162" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="E163" t="str">
+            <v>HGWDQ485SB6-84</v>
+          </cell>
+          <cell r="Y163" t="str">
+            <v>BPM</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="E164" t="str">
+            <v>HPGDL 8N1B-84</v>
+          </cell>
+          <cell r="Y164" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="E165" t="str">
+            <v>HPGDL 8N2B-84</v>
+          </cell>
+          <cell r="Y165" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="E166" t="str">
+            <v>HAMQD 410CBL9GN-84</v>
+          </cell>
+          <cell r="Y166" t="str">
+            <v>AC</v>
+          </cell>
+          <cell r="DM166">
+            <v>646</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="E167" t="str">
+            <v>HMQD 410CBL9-84</v>
+          </cell>
+          <cell r="Y167" t="str">
+            <v>AC</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="E168" t="str">
+            <v>HW80-B14367WU1</v>
+          </cell>
+          <cell r="Y168" t="str">
+            <v>DD</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="E169" t="str">
+            <v>NPI</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="1">
+          <cell r="Y1">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="Y2" t="str">
+            <v>Brutto Weight (KG)</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="Y3">
+            <v>66</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="Y4">
+            <v>70</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="Y5">
+            <v>38</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="Y6">
+            <v>70</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="Y7">
+            <v>55</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="Y8">
+            <v>94</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="Y9">
+            <v>114</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="Y10">
+            <v>118</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="Y11">
+            <v>117</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="Y12">
+            <v>111</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="Y13">
+            <v>94</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="Y14">
+            <v>78</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="Y15">
+            <v>103</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="Y16">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="Y17">
+            <v>81</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="Y18">
+            <v>85</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="Y19">
+            <v>75</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="Y20">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="Y21">
+            <v>114</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="Y22">
+            <v>111</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="Y23">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="Y24">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="Y25">
+            <v>89</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="Y26">
+            <v>96</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="Y27">
+            <v>96</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="Y28">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="Y29">
+            <v>93</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="Y30" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="Y31">
+            <v>134</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="Y32">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Y33">
+            <v>193</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="Y34">
+            <v>113</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="Y35">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="Y36">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="Y37">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="Y38">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="Y39">
+            <v>102</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="Y40">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="Y41">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="Y42">
+            <v>147</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="Y43">
+            <v>150</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="Y44">
+            <v>128</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="Y45">
+            <v>185</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="Y46">
+            <v>167</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="Y47">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="Y48">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="Y49">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="Y50">
+            <v>124</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="Y51">
+            <v>172</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="Y52">
+            <v>135</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="Y53">
+            <v>115</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="Y54">
+            <v>135</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="Y55">
+            <v>145</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="Y56">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="Y57">
+            <v>115</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="Y58">
+            <v>115</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="Y59">
+            <v>104</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="Y60">
+            <v>104</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="Y61">
+            <v>66</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="Y62">
+            <v>68</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="Y63">
+            <v>77</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="Y64">
+            <v>79</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="Y65">
+            <v>93</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="Y66">
+            <v>92.5</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="Y67">
+            <v>56.5</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="Y68">
+            <v>44</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="Y69">
+            <v>55.5</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="Y70">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="Y71">
+            <v>44</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="Y72">
+            <v>106</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="Y73" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="Y74" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="Y75" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="Y76" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="Y77" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="Y78" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="Y79" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="Y80" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="Y81" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="Y82" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="Y83" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="Y84" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="Y85" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="Y86" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="Y87" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="Y88" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="Y89" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="Y90" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="Y91" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="Y92">
+            <v>103</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="Y93">
+            <v>103</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="Y94" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="Y95" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="Y96" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="Y97" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="Y98" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="Y99" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="Y100">
+            <v>106</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="Y101">
+            <v>108</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="Y102">
+            <v>113</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="Y103" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="Y104">
+            <v>115</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="Y105">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="Y106">
+            <v>88</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="Y107">
+            <v>90</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="Y108">
+            <v>88</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="Y109">
+            <v>106</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="Y110">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="Y111">
+            <v>91</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="Y112">
+            <v>88</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="Y113" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="Y114">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="Y115">
+            <v>97</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="Y116">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="Y117">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="Y118">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="Y119" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="Y120">
+            <v>147</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="Y121">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="Y122">
+            <v>117</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="Y123">
+            <v>142</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="Y124">
+            <v>124</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="Y125">
+            <v>123</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="Y126">
+            <v>172</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="Y127">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="Y128">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="Y129">
+            <v>158</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="Y130">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="Y131">
+            <v>123</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="Y132">
+            <v>125</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="Y133">
+            <v>145</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="Y134">
+            <v>145</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="Y135">
+            <v>145</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="Y136" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="Y137">
+            <v>193</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="Y138">
+            <v>115</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="Y139">
+            <v>116</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="Y140">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="Y141">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="Y142">
+            <v>103</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="Y143">
+            <v>108</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="Y144" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="Y145">
+            <v>171</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="Y146">
+            <v>185</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="Y147">
+            <v>158</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="Y148">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="Y149">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="Y150" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="Y151" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="Y152">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="Y153">
+            <v>110</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="Y154">
+            <v>115</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="Y155">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="Y156">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="Y157" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="Y158" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="Y159">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="Y160" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="Y161">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="Y173">
+            <v>98</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="Y174">
+            <v>42.5</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="Y175">
+            <v>82</v>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="Y181">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="Y188">
+            <v>135</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="Y189" t="str">
+            <v>-</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="Y190">
+            <v>116.15</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="Y191">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="Y192">
+            <v>94</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="Y193">
+            <v>91</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="Y194">
+            <v>167</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5">
+        <row r="2">
+          <cell r="Y2" t="str">
+            <v>Energy label</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="Y3" t="str">
+            <v xml:space="preserve">A </v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="Y4" t="str">
+            <v>B</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="Y5" t="str">
+            <v>A-30</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="Y6" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="Y7" t="str">
+            <v>B</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="Y8" t="str">
+            <v>A</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="Y9" t="str">
+            <v>B</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="Y10" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="Y11" t="str">
+            <v>A</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="Y12" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="Y13" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="Y14" t="str">
+            <v>B</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="Y15" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="Y16" t="str">
+            <v>B</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="Y17" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="Y18" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="Y19" t="str">
+            <v>B</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="Y20" t="str">
+            <v>A</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="Y21" t="str">
+            <v>B</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="Y22" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="Y23" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="Y24" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="Y25" t="str">
+            <v>B</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="Y26" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="Y27" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="Y28" t="str">
+            <v>E</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="Y29" t="str">
+            <v>E</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6">
+        <row r="1">
+          <cell r="Y1">
+            <v>34006213</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="Y2" t="str">
+            <v>HSPR79F18DWMB</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="Y3" t="str">
+            <v>NPI 2026</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="Y4" t="str">
+            <v>SBS 3D</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="Y7" t="str">
+            <v>√</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="Y8" t="str">
+            <v>√</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="Y11" t="str">
+            <v>√</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="Y12" t="str">
+            <v>√</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="Y13" t="str">
+            <v>Water dispenser (with tank</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="Y14" t="str">
+            <v>√</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="Y16" t="str">
+            <v>√</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="Y18" t="str">
+            <v>√</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="Y19" t="str">
+            <v>√</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="Y21" t="str">
+            <v>√</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="Y24" t="str">
+            <v>Apr 2026</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="Y25">
+            <v>2098.5</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="Y26">
+            <v>1399</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="Y28">
+            <v>890</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="Y30">
+            <v>720</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="Y40">
+            <v>850</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="Y45" t="str">
+            <v>Fridge-freezer combination</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="Y46" t="str">
+            <v>Freestanding</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="Y47" t="str">
+            <v>Haier</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="Y48" t="str">
+            <v>Series 7</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="Y51" t="str">
+            <v>China</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="Y53" t="str">
+            <v>Black</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="Y54">
+            <v>90.5</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="Y55">
+            <v>177.5</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="Y56">
+            <v>70.7</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="Y57">
+            <v>97</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="Y58">
+            <v>96.7</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="Y59">
+            <v>188.2</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="Y60">
+            <v>77.5</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="Y61">
+            <v>105</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="Y62">
+            <v>48</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="Y63" t="str">
+            <v>Yes - front only</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="Y64" t="str">
+            <v>Fridge-freezer combination, hinge cover, egg tray, ice cube tray</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="Y65">
+            <v>220</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="Y66" t="str">
+            <v>4 stars</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="Y67">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="Y68">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="Y69" t="str">
+            <v>R600a</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="Y70">
+            <v>384</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="Y72" t="str">
+            <v>Automatic</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="Y73">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="Y74" t="str">
+            <v>Refrigerator compartment: 2 to 9 °C
+Freezer compartment: -14 to -24 °C</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="Y75">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="Y76">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="Y77">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="Y78">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="Y79" t="str">
+            <v>Glass</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="Y80" t="str">
+            <v>N/A</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="Y81" t="str">
+            <v>No</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="Y82" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="Y83" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="Y84">
+            <v>189</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="Y85" t="str">
+            <v>LEFT</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="Y86">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="Y87" t="str">
+            <v>Automatic</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="Y88" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="Y89" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="Y90" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="Y91" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="Y92" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="Y93" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="Y94" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="Y95" t="str">
+            <v>N/A</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="Y96">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="Y97" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="Y98" t="str">
+            <v>LED</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="Y100" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="Y101" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="Y102" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="Y103" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="Y104" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="Y105" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="Y106" t="str">
+            <v>None</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="Y107" t="str">
+            <v>None</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="Y108" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="Y109" t="str">
+            <v>None</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="Y110" t="str">
+            <v>exterternal touch display</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="Y111" t="str">
+            <v>Outside</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="Y112" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="Y113" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="Y114" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="Y115" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="Y116" t="str">
+            <v>Yes</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="Y117" t="str">
+            <v>220-240 Volt</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="Y118" t="str">
+            <v>50 Hz</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="Y121" t="str">
+            <v>Schuko</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="Y122" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="Y123" t="str">
+            <v>D</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="Y124" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="Y125" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="Y126" t="str">
+            <v>Freestanding</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="Y127" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="Y128">
+            <v>573</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="Y130">
+            <v>37</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="Y131" t="str">
+            <v>C</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="Y133" t="str">
+            <v xml:space="preserve"> SN.N.ST.T</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="Y134" t="str">
+            <v>10℃</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="Y135" t="str">
+            <v>43℃</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="Y136" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="Y137" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="Y138" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="Y139" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="Y140" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="Y141" t="str">
+            <v>384L</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="Y142" t="str">
+            <v>4℃</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="Y143" t="str">
+            <v>Automatic defrosting</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="Y144" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="Y145" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="Y146" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="Y147" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="Y148" t="str">
+            <v>No</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="Y149" t="str">
+            <v>No</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="Y150" t="str">
+            <v>No</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="Y151" t="str">
+            <v>No</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="Y152" t="str">
+            <v>Yes</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="Y153" t="str">
+            <v>103L</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="Y154" t="str">
+            <v>-18℃</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="Y155" t="str">
+            <v>Automatic defrosting</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="Y156">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="Y157" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="Y158" t="str">
+            <v>NO</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="Y159" t="str">
+            <v>YES</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="Y160" t="str">
+            <v>LED</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="Y161" t="str">
+            <v>F</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="Y162" t="str">
+            <v>6.55</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="Y163" t="str">
+            <v>3.209</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="Y164" t="str">
+            <v>0.0</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="Y165" t="str">
+            <v>0.0</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="Y166" t="str">
+            <v>0000.00</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="Y167" t="str">
+            <v>140.0</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="Y168" t="str">
+            <v>075</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="Y169" t="str">
+            <v>FR R600a</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7">
+        <row r="1">
+          <cell r="Y1">
+            <v>59</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="Y2" t="str">
+            <v>Height (gross / incl. packaging) mm</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="Y3">
+            <v>895</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="Y4">
+            <v>890</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="Y5">
+            <v>895</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="Y6">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="Y7">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="Y8">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="Y9">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="Y10">
+            <v>2159</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="Y11">
+            <v>2025</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="Y12">
+            <v>2072</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="Y13">
+            <v>1972</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="Y14">
+            <v>2072</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="Y15">
+            <v>1864</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="Y16">
+            <v>1864</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="Y17">
+            <v>1864</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="Y18">
+            <v>2025</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="Y19">
+            <v>2010</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="Y20">
+            <v>1905</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="Y21">
+            <v>1905</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="Y22">
+            <v>1882</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="Y23">
+            <v>1882</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="Y24">
+            <v>1882</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="Y25">
+            <v>1888</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="Y26">
+            <v>1888</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="Y27">
+            <v>1888</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="Y28">
+            <v>1888</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="Y29">
+            <v>1640</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="Y30">
+            <v>1640</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="Y31">
+            <v>1880</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="Y32">
+            <v>2005</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Y33">
+            <v>1880</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="Y34">
+            <v>2005</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="Y35">
+            <v>1330</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="Y36">
+            <v>880</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="Y37">
+            <v>1330</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="Y38">
+            <v>890</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="Y39">
+            <v>1320</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="Y40">
+            <v>2010</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="Y41">
+            <v>2015</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="Y42">
+            <v>2025</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="Y43">
+            <v>895</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="Y45">
+            <v>2010</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="Y46">
+            <v>2005</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="Y47">
+            <v>2005</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="Y48">
+            <v>2010</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="Y49">
+            <v>1944</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="Y50">
+            <v>1944</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="Y51">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="Y52">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="Y53">
+            <v>1944</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="Y54">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="Y55">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="Y56">
+            <v>1944</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="Y57">
+            <v>1944</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="Y58">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="Y59">
+            <v>2144</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="Y60">
+            <v>1864</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="Y61">
+            <v>1864</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="Y62">
+            <v>1935</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="Y63">
+            <v>1905</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="Y64">
+            <v>1905</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="Y65">
+            <v>1905</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="Y66">
+            <v>2010</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="Y67">
+            <v>2010</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="Y68">
+            <v>1882</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="Y69">
+            <v>1882</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="Y70">
+            <v>2010</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="Y71">
+            <v>1640</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="Y72">
+            <v>1320</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="Y73">
+            <v>2005</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="Y74">
+            <v>2005</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="Y77">
+            <v>1922</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="Y78">
+            <v>1922</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="Y79">
+            <v>1922</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="Y80">
+            <v>1894</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="Y81">
+            <v>1894</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="Y82">
+            <v>1894</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="Y83">
+            <v>1894</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="Y84">
+            <v>1894</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="Y85">
+            <v>1882</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="Y109">
+            <v>885</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="Y111">
+            <v>885</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="Y117">
+            <v>1474</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="Y118">
+            <v>1474</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="Y119">
+            <v>1474</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="Y120">
+            <v>1474</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="Y121">
+            <v>1820</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="Y122">
+            <v>1820</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="Y123">
+            <v>1820</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="Y124">
+            <v>1897</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="Y125">
+            <v>1897</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="Y126">
+            <v>1897</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="Y127">
+            <v>1897</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="Y128">
+            <v>1850</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="Y129">
+            <v>2050</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="Y130">
+            <v>2050</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="8">
+        <row r="2">
+          <cell r="D2" t="str">
+            <v>ARTICLE
+CODE</v>
+          </cell>
+          <cell r="Y2" t="str">
+            <v>Expert Strecke</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="D3">
+            <v>32901923</v>
+          </cell>
+          <cell r="Y3">
+            <v>445.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="D4">
+            <v>32901998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>32901835</v>
+          </cell>
+          <cell r="Y5">
+            <v>390.5</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="D6">
+            <v>32901822</v>
+          </cell>
+          <cell r="Y6">
+            <v>805</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="D7">
+            <v>32901911</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>32901912</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>32901900</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="D10">
+            <v>32901914</v>
+          </cell>
+          <cell r="Y10">
+            <v>307.5</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="D11">
+            <v>32901913</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="D12">
+            <v>32901901</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="D13">
+            <v>32901902</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="D14">
+            <v>32002769</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="D15">
+            <v>32002677</v>
+          </cell>
+          <cell r="Y15">
+            <v>311.5</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="D16">
+            <v>32002678</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="D17">
+            <v>32002680</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="D18">
+            <v>32002679</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="D19">
+            <v>32002670</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="D20">
+            <v>32002671</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="D21">
+            <v>32002672</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="D22">
+            <v>32901939</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="D23">
+            <v>32002663</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="D24">
+            <v>32901618</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25">
+            <v>32901591</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>32901647</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
+            <v>32901800</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="D28">
+            <v>32901457</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="D29">
+            <v>32002573</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="D30">
+            <v>32002576</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="D31">
+            <v>32002574</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="D32">
+            <v>32002639</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Y33" t="str">
+            <v>x</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="D34">
+            <v>34901816</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="D35">
+            <v>34901657</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="D36">
+            <v>34901727</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="D37">
+            <v>34901580</v>
+          </cell>
+          <cell r="Y37">
+            <v>692.5</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="D38">
+            <v>34901784</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="D39">
+            <v>34901783</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="D40">
+            <v>34901772</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="D41">
+            <v>34901756</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="D42">
+            <v>34901815</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="D43">
+            <v>37900612</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="D44">
+            <v>34901566</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="D45">
+            <v>34901564</v>
+          </cell>
+          <cell r="Y45">
+            <v>472</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="D46">
+            <v>34901712</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="D47">
+            <v>34901714</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="D48">
+            <v>34901646</v>
+          </cell>
+          <cell r="Y48">
+            <v>629.5</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="D49">
+            <v>34901808</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="D50">
+            <v>34901732</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="D51">
+            <v>34901731</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="D52">
+            <v>34901707</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="D53">
+            <v>34901706</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="D54">
+            <v>37900605</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="D55">
+            <v>34901572</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="D56">
+            <v>34901253</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="D57">
+            <v>34901246</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="D58">
+            <v>34901636</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="D59">
+            <v>34901611</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="D60">
+            <v>34901590</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="D61">
+            <v>34901601</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="D62">
+            <v>34901602</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="Y63" t="str">
+            <v>x</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="D64">
+            <v>33703946</v>
+          </cell>
+          <cell r="Y64">
+            <v>755.5</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="D65">
+            <v>33703938</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="D66">
+            <v>33703941</v>
+          </cell>
+          <cell r="Y66">
+            <v>629.5</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="D67">
+            <v>33703908</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="D68">
+            <v>33703811</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="D69">
+            <v>33703808</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="D70">
+            <v>33703990</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="D71">
+            <v>33704273</v>
+          </cell>
+          <cell r="Y71">
+            <v>261.5</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="D72">
+            <v>33703792</v>
+          </cell>
+          <cell r="Y72">
+            <v>314.5</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="D73">
+            <v>33704557</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="D74">
+            <v>33704556</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="D75">
+            <v>33703874</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="D76">
+            <v>33703862</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="D77">
+            <v>33703851</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="D78">
+            <v>33703956</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="D79">
+            <v>33704458</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="D80">
+            <v>33704188</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="D81">
+            <v>33900632</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="D82">
+            <v>33900635</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="D83">
+            <v>33900634</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="D84">
+            <v>33900652</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="Y85" t="str">
+            <v>x</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="D86">
+            <v>38900825</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="D87">
+            <v>38900827</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="D88">
+            <v>38900826</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="Y89" t="str">
+            <v>x</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="D90">
+            <v>33803037</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="D91">
+            <v>33803469</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="D92">
+            <v>33803399</v>
+          </cell>
+          <cell r="Y92">
+            <v>377.5</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="D93">
+            <v>33803413</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="D94">
+            <v>33803608</v>
+          </cell>
+          <cell r="Y94">
+            <v>200</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="D95">
+            <v>33803688</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="D96">
+            <v>33803689</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="D97">
+            <v>33803416</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="D98">
+            <v>33803338</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="D99">
+            <v>33803265</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="D100">
+            <v>33803666</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="D101">
+            <v>33801793</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="D102">
+            <v>33802915</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="D103">
+            <v>33802918</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="D104">
+            <v>33803260</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="D105">
+            <v>33803263</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="D106">
+            <v>33803686</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="D107">
+            <v>33803136</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="Y108" t="str">
+            <v>x</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="D109">
+            <v>36901930</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="D110">
+            <v>36901921</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="D111">
+            <v>36901774</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="D112">
+            <v>36901769</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="D113">
+            <v>36901044</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="D114">
+            <v>36901776</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="D115">
+            <v>36901681</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="D117">
+            <v>31800951</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="D118">
+            <v>31800949</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="D119">
+            <v>31801014</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="D120">
+            <v>31801018</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="D121">
+            <v>33702981</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="D122">
+            <v>33703384</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="D123">
+            <v>33703383</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="D124">
+            <v>33803406</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="D125">
+            <v>33803082</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="D126">
+            <v>33803111</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="D127">
+            <v>33802774</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="D128">
+            <v>33803015</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="D129">
+            <v>32901793</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="D130">
+            <v>32901794</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="D131">
+            <v>32901750</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="D132">
+            <v>32901570</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="D133">
+            <v>32901795</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="D134">
+            <v>34901398</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="D135">
+            <v>34901396</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="D136">
+            <v>34901708</v>
+          </cell>
+          <cell r="Y136">
+            <v>1071</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="D137">
+            <v>34901709</v>
+          </cell>
+          <cell r="Y137">
+            <v>1890</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="D138">
+            <v>34901569</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="D139">
+            <v>38900737</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="D140">
+            <v>38900763</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="D141">
+            <v>38900021</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="D142">
+            <v>36901711</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="D143">
+            <v>36901780</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="D144">
+            <v>36901781</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9">
+        <row r="4">
+          <cell r="Y4" t="str">
+            <v>Comment</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="Y23" t="str">
+            <v>Horizon</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="Y32" t="str">
+            <v>Horizon</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Y33" t="str">
+            <v>Horizon</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="Y34" t="str">
+            <v>Horizon</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="Y93" t="str">
+            <v>Horizon</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10">
+        <row r="2">
+          <cell r="Y2" t="str">
+            <v>Expert</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="Y3">
+            <v>725.45</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="Y5">
+            <v>612</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="Y35" t="str">
+            <v>Angebot:
+629</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12">
+        <row r="3">
+          <cell r="Y3" t="str">
+            <v>GROSS WEIGHT (in kg)</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="Y4">
+            <v>3.38</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="Y5">
+            <v>3.37</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="Y6">
+            <v>0.9</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="Y7">
+            <v>0.13500000000000001</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="Y8">
+            <v>0.14000000000000001</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="Y9">
+            <v>0.81</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="Y10">
+            <v>0.64100000000000001</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="Y11">
+            <v>0.17299999999999999</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="Y12">
+            <v>0.54500000000000004</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="Y13">
+            <v>0.42</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="Y14">
+            <v>0.115</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="Y15">
+            <v>0.9</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="Y16">
+            <v>0.33</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="Y17">
+            <v>0.63</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="Y19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="Y20">
+            <v>1.7</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="Y21">
+            <v>0.13</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="Y22">
+            <v>0.53</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="Y23">
+            <v>0.53</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="Y24">
+            <v>0.52</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="Y25">
+            <v>0.52</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="Y26">
+            <v>0.52</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="Y27">
+            <v>0.52</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="Y28">
+            <v>0.52</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="Y29">
+            <v>0.52</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="Y30">
+            <v>1.4</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="Y31">
+            <v>0.75</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="Y32">
+            <v>0.32</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="Y33">
+            <v>1.4</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="Y34">
+            <v>0.13500000000000001</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="Y35">
+            <v>0.48</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="Y36">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="Y37">
+            <v>0.48</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="Y38">
+            <v>0.35</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="Y39">
+            <v>0.68</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="Y40">
+            <v>3.43</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="Y41">
+            <v>1.1950000000000001</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="Y42">
+            <v>1.2969999999999999</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="Y43">
+            <v>0.25</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="Y44">
+            <v>0.18</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="Y45">
+            <v>0.31</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="Y46">
+            <v>0.86</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="Y47">
+            <v>0.53</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="Y48">
+            <v>8.9999999999999993E-3</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="Y49">
+            <v>1.6</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="Y50">
+            <v>0.81</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="Y51">
+            <v>0.83</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="Y52">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="Y53">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="Y55">
+            <v>0.2</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="Y56">
+            <v>0.34</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="Y57">
+            <v>0.15</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="Y58">
+            <v>0.03</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="Y59">
+            <v>0.155</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="Y60">
+            <v>3.39</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="Y61">
+            <v>0.33</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="Y62">
+            <v>0.46</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="Y63">
+            <v>0.35</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="Y64">
+            <v>0.05</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="Y65">
+            <v>0.2</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="Y66">
+            <v>0.45</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="Y67">
+            <v>0.13500000000000001</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="Y68">
+            <v>0.13500000000000001</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="Y69">
+            <v>0.13500000000000001</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="Y70">
+            <v>0.13500000000000001</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="Y71">
+            <v>0.48</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="Y72">
+            <v>0.48</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="Y73">
+            <v>0.48</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="Y74">
+            <v>0.875</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="Y75">
+            <v>0.75</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="Y76">
+            <v>0.1</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="Y77">
+            <v>0.1</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="Y78">
+            <v>0.18</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="Y79">
+            <v>0.95</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="Y80">
+            <v>0.76</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="Y81">
+            <v>0.11</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="Y82">
+            <v>0.31</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="Y83">
+            <v>0.11799999999999999</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="Y84">
+            <v>0.6</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="Y85">
+            <v>0.6</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="Y86">
+            <v>8.9999999999999993E-3</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="Y87">
+            <v>0.57999999999999996</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="Y88">
+            <v>0.96</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="Y89">
+            <v>0.59</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="Y90">
+            <v>0.55000000000000004</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="Y91">
+            <v>0.59</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="Y92">
+            <v>0.57999999999999996</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="Y93">
+            <v>0.64</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="Y94">
+            <v>0.6</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="Y95">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="Y96">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="Y97">
+            <v>0.33</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="Y98">
+            <v>0.33</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="Y99">
+            <v>0.35</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="Y100">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="Y101">
+            <v>0.4</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="Y102">
+            <v>0.48</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="Y103">
+            <v>0.56000000000000005</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="Y104">
+            <v>0.45</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="Y105">
+            <v>0.41</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="Y106">
+            <v>0.47</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="Y107">
+            <v>0.54</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="Y108">
+            <v>0.63</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="Y109">
+            <v>0.68</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="Y110">
+            <v>1.45</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="Y111">
+            <v>1.26</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="Y112">
+            <v>0.31</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="Y113">
+            <v>0.55000000000000004</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="Y114">
+            <v>0.71</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="Y115">
+            <v>0.05</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="Y116">
+            <v>0.57999999999999996</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="Y117">
+            <v>0.56999999999999995</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="Y118">
+            <v>0.1</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="Y119">
+            <v>0.59</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="Y120">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="Y121">
+            <v>9.5000000000000001E-2</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="Y122">
+            <v>0.495</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="Y123">
+            <v>0.16500000000000001</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="Y124">
+            <v>5.9</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="Y125">
+            <v>0.61499999999999999</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="Y126">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="Y127">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="Y128">
+            <v>0.25</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="Y129">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="Y130">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="Y131">
+            <v>0.27</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="Y132">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="Y133">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="Y134" t="str">
+            <v>   0,598</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="Y135">
+            <v>0.33</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -967,55 +6938,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D870034-242D-49C0-BE89-40E84D61E957}">
-  <dimension ref="A1:U57"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U78"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="26.88671875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="30.109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="30.109375" style="20" customWidth="1"/>
-    <col min="7" max="7" width="30.109375" style="17" customWidth="1"/>
-    <col min="8" max="8" width="30.109375" style="7" customWidth="1"/>
-    <col min="9" max="9" width="26.88671875" style="13" customWidth="1"/>
-    <col min="10" max="22" width="11.109375" customWidth="1"/>
+    <col min="1" max="4" width="26.85546875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" style="20" customWidth="1"/>
+    <col min="7" max="7" width="30.140625" style="17" customWidth="1"/>
+    <col min="8" max="8" width="30.140625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="26.85546875" style="13" customWidth="1"/>
+    <col min="10" max="22" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G1" s="15"/>
       <c r="H1" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D2" s="8">
         <v>37001614</v>
@@ -1024,11 +6995,11 @@
         <v>2</v>
       </c>
       <c r="F2" s="19">
-        <v>178.00800000000001</v>
+        <v>240</v>
       </c>
       <c r="G2" s="16">
         <f>ROUND(F2,2)</f>
-        <v>178.01</v>
+        <v>240</v>
       </c>
       <c r="H2" s="8">
         <v>24</v>
@@ -1040,15 +7011,15 @@
       <c r="K2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D3" s="8">
         <v>37001627</v>
@@ -1057,11 +7028,11 @@
         <v>5</v>
       </c>
       <c r="F3" s="19">
-        <v>326.34800000000001</v>
+        <v>440</v>
       </c>
       <c r="G3" s="16">
-        <f t="shared" ref="G3:G57" si="0">ROUND(F3,2)</f>
-        <v>326.35000000000002</v>
+        <f>ROUND(F3,2)</f>
+        <v>440</v>
       </c>
       <c r="H3" s="8">
         <v>24</v>
@@ -1072,15 +7043,15 @@
       <c r="J3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" s="8">
         <v>34005713</v>
@@ -1089,11 +7060,11 @@
         <v>8</v>
       </c>
       <c r="F4" s="19">
-        <v>623.76970000000006</v>
+        <v>841</v>
       </c>
       <c r="G4" s="16">
-        <f t="shared" si="0"/>
-        <v>623.77</v>
+        <f>ROUND(F4,2)</f>
+        <v>841</v>
       </c>
       <c r="H4" s="8">
         <v>12</v>
@@ -1104,15 +7075,15 @@
       <c r="J4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="8">
         <v>34005731</v>
@@ -1121,11 +7092,11 @@
         <v>12</v>
       </c>
       <c r="F5" s="19">
-        <v>630.44500000000005</v>
+        <v>850</v>
       </c>
       <c r="G5" s="16">
-        <f t="shared" si="0"/>
-        <v>630.45000000000005</v>
+        <f>ROUND(F5,2)</f>
+        <v>850</v>
       </c>
       <c r="H5" s="8">
         <v>12</v>
@@ -1136,15 +7107,15 @@
       <c r="J5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="8">
         <v>34005843</v>
@@ -1153,11 +7124,11 @@
         <v>13</v>
       </c>
       <c r="F6" s="19">
-        <v>348.59899999999999</v>
+        <v>470</v>
       </c>
       <c r="G6" s="16">
-        <f t="shared" si="0"/>
-        <v>348.6</v>
+        <f>ROUND(F6,2)</f>
+        <v>470</v>
       </c>
       <c r="H6" s="8">
         <v>24</v>
@@ -1168,15 +7139,15 @@
       <c r="J6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D7" s="8">
         <v>34005705</v>
@@ -1185,11 +7156,11 @@
         <v>14</v>
       </c>
       <c r="F7" s="19">
-        <v>852.95500000000004</v>
+        <v>1150</v>
       </c>
       <c r="G7" s="16">
-        <f t="shared" si="0"/>
-        <v>852.96</v>
+        <f>ROUND(F7,2)</f>
+        <v>1150</v>
       </c>
       <c r="H7" s="8">
         <v>24</v>
@@ -1200,15 +7171,15 @@
       <c r="J7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" s="8">
         <v>34005708</v>
@@ -1217,11 +7188,11 @@
         <v>15</v>
       </c>
       <c r="F8" s="19">
-        <v>778.78500000000008</v>
+        <v>1050</v>
       </c>
       <c r="G8" s="16">
-        <f t="shared" si="0"/>
-        <v>778.79</v>
+        <f>ROUND(F8,2)</f>
+        <v>1050</v>
       </c>
       <c r="H8" s="8">
         <v>24</v>
@@ -1232,15 +7203,15 @@
       <c r="J8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" s="8">
         <v>37001606</v>
@@ -1249,11 +7220,11 @@
         <v>16</v>
       </c>
       <c r="F9" s="19">
-        <v>259.59500000000003</v>
+        <v>350</v>
       </c>
       <c r="G9" s="16">
-        <f t="shared" si="0"/>
-        <v>259.60000000000002</v>
+        <f>ROUND(F9,2)</f>
+        <v>350</v>
       </c>
       <c r="H9" s="8">
         <v>12</v>
@@ -1270,15 +7241,15 @@
       <c r="T9" s="2"/>
       <c r="U9" s="4"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10" s="8">
         <v>37001607</v>
@@ -1287,11 +7258,11 @@
         <v>17</v>
       </c>
       <c r="F10" s="19">
-        <v>296.68</v>
+        <v>400</v>
       </c>
       <c r="G10" s="16">
-        <f t="shared" si="0"/>
-        <v>296.68</v>
+        <f>ROUND(F10,2)</f>
+        <v>400</v>
       </c>
       <c r="H10" s="8">
         <v>12</v>
@@ -1302,15 +7273,15 @@
       <c r="J10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11" s="8">
         <v>37001609</v>
@@ -1319,11 +7290,11 @@
         <v>18</v>
       </c>
       <c r="F11" s="19">
-        <v>348.59899999999999</v>
+        <v>470</v>
       </c>
       <c r="G11" s="16">
-        <f t="shared" si="0"/>
-        <v>348.6</v>
+        <f>ROUND(F11,2)</f>
+        <v>470</v>
       </c>
       <c r="H11" s="8">
         <v>12</v>
@@ -1334,15 +7305,15 @@
       <c r="J11" s="1"/>
       <c r="M11" s="1"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" s="8">
         <v>37001610</v>
@@ -1351,11 +7322,11 @@
         <v>19</v>
       </c>
       <c r="F12" s="19">
-        <v>430.18600000000004</v>
+        <v>580</v>
       </c>
       <c r="G12" s="16">
-        <f t="shared" si="0"/>
-        <v>430.19</v>
+        <f>ROUND(F12,2)</f>
+        <v>580</v>
       </c>
       <c r="H12" s="8">
         <v>12</v>
@@ -1368,15 +7339,15 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D13" s="8">
         <v>34004290</v>
@@ -1385,11 +7356,11 @@
         <v>20</v>
       </c>
       <c r="F13" s="19">
-        <v>419.06049999999999</v>
+        <v>565</v>
       </c>
       <c r="G13" s="16">
-        <f t="shared" si="0"/>
-        <v>419.06</v>
+        <f>ROUND(F13,2)</f>
+        <v>565</v>
       </c>
       <c r="H13" s="8">
         <v>12</v>
@@ -1400,15 +7371,15 @@
       <c r="J13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="8">
         <v>34005568</v>
@@ -1417,11 +7388,11 @@
         <v>21</v>
       </c>
       <c r="F14" s="19">
-        <v>267.012</v>
+        <v>360</v>
       </c>
       <c r="G14" s="16">
-        <f t="shared" si="0"/>
-        <v>267.01</v>
+        <f>ROUND(F14,2)</f>
+        <v>360</v>
       </c>
       <c r="H14" s="8">
         <v>12</v>
@@ -1432,15 +7403,15 @@
       <c r="J14" s="1"/>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D15" s="8">
         <v>37001737</v>
@@ -1449,11 +7420,11 @@
         <v>22</v>
       </c>
       <c r="F15" s="19">
-        <v>259.59500000000003</v>
+        <v>350</v>
       </c>
       <c r="G15" s="16">
-        <f t="shared" si="0"/>
-        <v>259.60000000000002</v>
+        <f>ROUND(F15,2)</f>
+        <v>350</v>
       </c>
       <c r="H15" s="8">
         <v>24</v>
@@ -1464,15 +7435,15 @@
       <c r="J15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D16" s="8">
         <v>34005943</v>
@@ -1481,11 +7452,11 @@
         <v>23</v>
       </c>
       <c r="F16" s="19">
-        <v>793.61900000000003</v>
+        <v>1070</v>
       </c>
       <c r="G16" s="16">
-        <f t="shared" si="0"/>
-        <v>793.62</v>
+        <f>ROUND(F16,2)</f>
+        <v>1070</v>
       </c>
       <c r="H16" s="8">
         <v>24</v>
@@ -1496,15 +7467,15 @@
       <c r="J16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17" s="8">
         <v>37001683</v>
@@ -1513,11 +7484,11 @@
         <v>24</v>
       </c>
       <c r="F17" s="19">
-        <v>615.61099999999999</v>
+        <v>830</v>
       </c>
       <c r="G17" s="16">
-        <f t="shared" si="0"/>
-        <v>615.61</v>
+        <f>ROUND(F17,2)</f>
+        <v>830</v>
       </c>
       <c r="H17" s="8">
         <v>12</v>
@@ -1528,15 +7499,15 @@
       <c r="J17" s="1"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D18" s="8">
         <v>34005861</v>
@@ -1545,11 +7516,11 @@
         <v>25</v>
       </c>
       <c r="F18" s="19">
-        <v>452.43700000000001</v>
+        <v>610</v>
       </c>
       <c r="G18" s="16">
-        <f t="shared" si="0"/>
-        <v>452.44</v>
+        <f>ROUND(F18,2)</f>
+        <v>610</v>
       </c>
       <c r="H18" s="8">
         <v>12</v>
@@ -1560,15 +7531,15 @@
       <c r="J18" s="1"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D19" s="8">
         <v>34005971</v>
@@ -1577,11 +7548,11 @@
         <v>26</v>
       </c>
       <c r="F19" s="19">
-        <v>964.21</v>
+        <v>1300</v>
       </c>
       <c r="G19" s="16">
-        <f t="shared" si="0"/>
-        <v>964.21</v>
+        <f>ROUND(F19,2)</f>
+        <v>1300</v>
       </c>
       <c r="H19" s="8">
         <v>24</v>
@@ -1592,15 +7563,15 @@
       <c r="J19" s="1"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D20" s="8">
         <v>34006051</v>
@@ -1609,11 +7580,11 @@
         <v>27</v>
       </c>
       <c r="F20" s="19">
-        <v>496.93900000000002</v>
+        <v>670</v>
       </c>
       <c r="G20" s="16">
-        <f t="shared" si="0"/>
-        <v>496.94</v>
+        <f>ROUND(F20,2)</f>
+        <v>670</v>
       </c>
       <c r="H20" s="8">
         <v>12</v>
@@ -1624,15 +7595,15 @@
       <c r="J20" s="1"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21" s="8">
         <v>34006117</v>
@@ -1641,11 +7612,11 @@
         <v>28</v>
       </c>
       <c r="F21" s="19">
-        <v>281.846</v>
+        <v>380</v>
       </c>
       <c r="G21" s="16">
-        <f t="shared" si="0"/>
-        <v>281.85000000000002</v>
+        <f>ROUND(F21,2)</f>
+        <v>380</v>
       </c>
       <c r="H21" s="8">
         <v>12</v>
@@ -1656,15 +7627,15 @@
       <c r="J21" s="1"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D22" s="8">
         <v>34006058</v>
@@ -1673,11 +7644,11 @@
         <v>29</v>
       </c>
       <c r="F22" s="19">
-        <v>459.85400000000004</v>
+        <v>620</v>
       </c>
       <c r="G22" s="16">
-        <f t="shared" si="0"/>
-        <v>459.85</v>
+        <f>ROUND(F22,2)</f>
+        <v>620</v>
       </c>
       <c r="H22" s="8">
         <v>24</v>
@@ -1688,91 +7659,95 @@
       <c r="J22" s="1"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D23" s="8">
-        <v>34006220</v>
+        <v>34901580</v>
       </c>
       <c r="E23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="19">
+        <v>692.65</v>
+      </c>
+      <c r="G23" s="16">
+        <v>692.5</v>
+      </c>
+      <c r="H23" s="8">
+        <v>12</v>
+      </c>
+      <c r="I23" s="10">
+        <v>2</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="M23" cm="1">
+        <f t="array" ref="M23">_xlfn.XLOOKUP(D23,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>692.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="19">
-        <v>593.36</v>
-      </c>
-      <c r="G23" s="16">
-        <f t="shared" si="0"/>
-        <v>593.36</v>
-      </c>
-      <c r="H23" s="8">
-        <v>24</v>
-      </c>
-      <c r="I23" s="9">
-        <v>1</v>
-      </c>
-      <c r="J23" s="1"/>
-      <c r="M23" s="1"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="B24" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" s="8">
-        <v>34901580</v>
+        <v>34901646</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="19">
-        <v>692.65</v>
+        <v>629.62</v>
       </c>
       <c r="G24" s="16">
-        <f t="shared" si="0"/>
-        <v>692.65</v>
+        <v>629.5</v>
       </c>
       <c r="H24" s="8">
         <v>12</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="11">
         <v>2</v>
       </c>
       <c r="J24" s="1"/>
+      <c r="M24" cm="1">
+        <f t="array" ref="M24">_xlfn.XLOOKUP(D24,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>629.5</v>
+      </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" s="8">
-        <v>34901646</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>33</v>
+        <v>34901708</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="F25" s="19">
-        <v>629.62</v>
+        <v>1070.8</v>
       </c>
       <c r="G25" s="16">
-        <f t="shared" si="0"/>
-        <v>629.62</v>
+        <v>1071</v>
       </c>
       <c r="H25" s="8">
         <v>12</v>
@@ -1781,29 +7756,32 @@
         <v>2</v>
       </c>
       <c r="J25" s="1"/>
+      <c r="M25" cm="1">
+        <f t="array" ref="M25">_xlfn.XLOOKUP(D25,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>1071</v>
+      </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D26" s="8">
-        <v>34901708</v>
+        <v>34901709</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F26" s="19">
-        <v>1070.8</v>
+        <v>1890.13</v>
       </c>
       <c r="G26" s="16">
-        <f t="shared" si="0"/>
-        <v>1070.8</v>
+        <v>1890</v>
       </c>
       <c r="H26" s="8">
         <v>12</v>
@@ -1812,91 +7790,101 @@
         <v>2</v>
       </c>
       <c r="J26" s="1"/>
+      <c r="M26" cm="1">
+        <f t="array" ref="M26">_xlfn.XLOOKUP(D26,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>1890</v>
+      </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" s="8">
-        <v>34901709</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>80</v>
+        <v>34901564</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="F27" s="19">
-        <v>1890.13</v>
+        <v>472.06</v>
       </c>
       <c r="G27" s="16">
-        <f t="shared" si="0"/>
-        <v>1890.13</v>
+        <v>472</v>
       </c>
       <c r="H27" s="8">
         <v>12</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="10">
         <v>2</v>
       </c>
       <c r="J27" s="1"/>
+      <c r="M27" cm="1">
+        <f t="array" ref="M27">_xlfn.XLOOKUP(D27,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>472</v>
+      </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D28" s="8">
-        <v>34901564</v>
+        <v>33703946</v>
       </c>
       <c r="E28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="19">
+        <v>755.67</v>
+      </c>
+      <c r="G28" s="16">
+        <v>755.5</v>
+      </c>
+      <c r="H28" s="8">
+        <v>4</v>
+      </c>
+      <c r="I28" s="11">
+        <v>6</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="M28" cm="1">
+        <f t="array" ref="M28">_xlfn.XLOOKUP(D28,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>755.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="F28" s="19">
-        <v>472.06</v>
-      </c>
-      <c r="G28" s="16">
-        <f t="shared" si="0"/>
-        <v>472.06</v>
-      </c>
-      <c r="H28" s="8">
-        <v>12</v>
-      </c>
-      <c r="I28" s="10">
-        <v>2</v>
-      </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D29" s="8">
-        <v>33703946</v>
+        <v>33703941</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>36</v>
       </c>
       <c r="F29" s="19">
-        <v>755.67</v>
+        <v>646.41</v>
       </c>
       <c r="G29" s="16">
-        <f t="shared" si="0"/>
-        <v>755.67</v>
+        <v>629.5</v>
       </c>
       <c r="H29" s="8">
         <v>4</v>
@@ -1906,29 +7894,32 @@
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
+      <c r="M29" cm="1">
+        <f t="array" ref="M29">_xlfn.XLOOKUP(D29,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>629.5</v>
+      </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D30" s="8">
-        <v>33703941</v>
+        <v>33704273</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>37</v>
       </c>
       <c r="F30" s="19">
-        <v>646.41</v>
+        <v>261.52999999999997</v>
       </c>
       <c r="G30" s="16">
-        <f t="shared" si="0"/>
-        <v>646.41</v>
+        <v>261.5</v>
       </c>
       <c r="H30" s="8">
         <v>4</v>
@@ -1938,29 +7929,32 @@
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
+      <c r="M30" cm="1">
+        <f t="array" ref="M30">_xlfn.XLOOKUP(D30,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>261.5</v>
+      </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D31" s="8">
-        <v>33704273</v>
+        <v>33703792</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>38</v>
       </c>
       <c r="F31" s="19">
-        <v>261.52999999999997</v>
+        <v>314.5</v>
       </c>
       <c r="G31" s="16">
-        <f t="shared" si="0"/>
-        <v>261.52999999999997</v>
+        <v>314.5</v>
       </c>
       <c r="H31" s="8">
         <v>4</v>
@@ -1970,125 +7964,137 @@
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
+      <c r="M31" cm="1">
+        <f t="array" ref="M31">_xlfn.XLOOKUP(D31,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>314.5</v>
+      </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D32" s="8">
-        <v>33703792</v>
+        <v>33803608</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>39</v>
       </c>
       <c r="F32" s="19">
-        <v>314.5</v>
+        <v>188.45</v>
       </c>
       <c r="G32" s="16">
-        <f t="shared" si="0"/>
-        <v>314.5</v>
+        <v>200</v>
       </c>
       <c r="H32" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I32" s="11">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
+      <c r="M32" cm="1">
+        <f t="array" ref="M32">_xlfn.XLOOKUP(D32,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>200</v>
+      </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D33" s="8">
-        <v>33803608</v>
+        <v>33803399</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>40</v>
       </c>
       <c r="F33" s="19">
-        <v>188.45</v>
+        <v>377.52</v>
       </c>
       <c r="G33" s="16">
-        <f t="shared" si="0"/>
-        <v>188.45</v>
+        <v>377.5</v>
       </c>
       <c r="H33" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33" s="11">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
+      <c r="M33" cm="1">
+        <f t="array" ref="M33">_xlfn.XLOOKUP(D33,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>377.5</v>
+      </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D34" s="8">
-        <v>33803399</v>
+        <v>32901822</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F34" s="19">
-        <v>377.52</v>
+        <v>724.16</v>
       </c>
       <c r="G34" s="16">
-        <f t="shared" si="0"/>
-        <v>377.52</v>
+        <v>805</v>
       </c>
       <c r="H34" s="8">
+        <v>6</v>
+      </c>
+      <c r="I34" s="10">
         <v>4</v>
-      </c>
-      <c r="I34" s="11">
-        <v>6</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
+      <c r="M34" cm="1">
+        <f t="array" ref="M34">_xlfn.XLOOKUP(D34,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>805</v>
+      </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D35" s="8">
-        <v>32901822</v>
+        <v>32901835</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F35" s="19">
-        <v>724.16</v>
+        <v>392.62</v>
       </c>
       <c r="G35" s="16">
-        <f t="shared" si="0"/>
-        <v>724.16</v>
+        <v>390.5</v>
       </c>
       <c r="H35" s="8">
         <v>6</v>
@@ -2098,29 +8104,32 @@
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
+      <c r="M35" cm="1">
+        <f t="array" ref="M35">_xlfn.XLOOKUP(D35,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>390.5</v>
+      </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D36" s="8">
-        <v>32901835</v>
+        <v>32002677</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F36" s="19">
-        <v>392.62</v>
+        <v>311.35000000000002</v>
       </c>
       <c r="G36" s="16">
-        <f t="shared" si="0"/>
-        <v>392.62</v>
+        <v>311.5</v>
       </c>
       <c r="H36" s="8">
         <v>6</v>
@@ -2130,29 +8139,32 @@
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
+      <c r="M36" cm="1">
+        <f t="array" ref="M36">_xlfn.XLOOKUP(D36,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>311.5</v>
+      </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D37" s="8">
-        <v>32002677</v>
+        <v>32901914</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>45</v>
       </c>
       <c r="F37" s="19">
-        <v>311.35000000000002</v>
+        <v>307.41000000000003</v>
       </c>
       <c r="G37" s="16">
-        <f t="shared" si="0"/>
-        <v>311.35000000000002</v>
+        <v>307.5</v>
       </c>
       <c r="H37" s="8">
         <v>6</v>
@@ -2162,61 +8174,68 @@
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
+      <c r="M37" cm="1">
+        <f t="array" ref="M37">_xlfn.XLOOKUP(D37,'[1]CBI all'!$D:$D,[1]!EXP_CBI)</f>
+        <v>307.5</v>
+      </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D38" s="8">
-        <v>32901914</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>46</v>
+        <v>90</v>
+      </c>
+      <c r="D38" s="7">
+        <v>31021286</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="F38" s="19">
-        <v>307.41000000000003</v>
+        <v>225</v>
       </c>
       <c r="G38" s="16">
-        <f t="shared" si="0"/>
-        <v>307.41000000000003</v>
+        <f>ROUND(F38,2)</f>
+        <v>225</v>
       </c>
       <c r="H38" s="8">
         <v>6</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="12">
         <v>4</v>
       </c>
-      <c r="J38" s="1"/>
       <c r="K38" s="1"/>
+      <c r="M38">
+        <f>_xlfn.XLOOKUP(E38,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>225</v>
+      </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D39" s="7">
-        <v>31021286</v>
+        <v>31021444</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>48</v>
       </c>
       <c r="F39" s="19">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G39" s="16">
-        <f t="shared" si="0"/>
-        <v>225</v>
+        <f>ROUND(F39,2)</f>
+        <v>239</v>
       </c>
       <c r="H39" s="8">
         <v>6</v>
@@ -2226,28 +8245,28 @@
       </c>
       <c r="K39" s="1"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D40" s="7">
-        <v>31021444</v>
+        <v>31021288</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>49</v>
       </c>
       <c r="F40" s="19">
-        <v>239</v>
+        <v>289</v>
       </c>
       <c r="G40" s="16">
-        <f t="shared" si="0"/>
-        <v>239</v>
+        <f>ROUND(F40,2)</f>
+        <v>289</v>
       </c>
       <c r="H40" s="8">
         <v>6</v>
@@ -2256,29 +8275,33 @@
         <v>4</v>
       </c>
       <c r="K40" s="1"/>
+      <c r="M40">
+        <f>_xlfn.XLOOKUP(E40,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>289</v>
+      </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D41" s="7">
-        <v>31021288</v>
+        <v>31021290</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>50</v>
       </c>
       <c r="F41" s="19">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="G41" s="16">
-        <f t="shared" si="0"/>
-        <v>289</v>
+        <f>ROUND(F41,2)</f>
+        <v>297</v>
       </c>
       <c r="H41" s="8">
         <v>6</v>
@@ -2287,29 +8310,33 @@
         <v>4</v>
       </c>
       <c r="K41" s="1"/>
+      <c r="M41">
+        <f>_xlfn.XLOOKUP(E41,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>297</v>
+      </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D42" s="7">
-        <v>31021290</v>
+        <v>31021291</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>51</v>
       </c>
       <c r="F42" s="19">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="G42" s="16">
-        <f t="shared" si="0"/>
-        <v>297</v>
+        <f>ROUND(F42,2)</f>
+        <v>309</v>
       </c>
       <c r="H42" s="8">
         <v>6</v>
@@ -2318,29 +8345,33 @@
         <v>4</v>
       </c>
       <c r="K42" s="1"/>
+      <c r="M42">
+        <f>_xlfn.XLOOKUP(E42,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>309</v>
+      </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D43" s="7">
-        <v>31021291</v>
+        <v>31021294</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>52</v>
       </c>
       <c r="F43" s="19">
-        <v>309</v>
+        <v>375</v>
       </c>
       <c r="G43" s="16">
-        <f t="shared" si="0"/>
-        <v>309</v>
+        <f>ROUND(F43,2)</f>
+        <v>375</v>
       </c>
       <c r="H43" s="8">
         <v>6</v>
@@ -2349,29 +8380,33 @@
         <v>4</v>
       </c>
       <c r="K43" s="1"/>
+      <c r="M43">
+        <f>_xlfn.XLOOKUP(E43,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>375</v>
+      </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D44" s="7">
-        <v>31021294</v>
+        <v>31021295</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>53</v>
       </c>
       <c r="F44" s="19">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="G44" s="16">
-        <f t="shared" si="0"/>
-        <v>375</v>
+        <f>ROUND(F44,2)</f>
+        <v>399</v>
       </c>
       <c r="H44" s="8">
         <v>6</v>
@@ -2380,29 +8415,33 @@
         <v>4</v>
       </c>
       <c r="K44" s="1"/>
+      <c r="M44">
+        <f>_xlfn.XLOOKUP(E44,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>399</v>
+      </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D45" s="7">
-        <v>31021295</v>
+        <v>31021298</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>54</v>
       </c>
       <c r="F45" s="19">
-        <v>399</v>
+        <v>582</v>
       </c>
       <c r="G45" s="16">
-        <f t="shared" si="0"/>
-        <v>399</v>
+        <f>ROUND(F45,2)</f>
+        <v>582</v>
       </c>
       <c r="H45" s="8">
         <v>6</v>
@@ -2411,29 +8450,33 @@
         <v>4</v>
       </c>
       <c r="K45" s="1"/>
+      <c r="M45">
+        <f>_xlfn.XLOOKUP(E45,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>582</v>
+      </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D46" s="7">
-        <v>31021298</v>
+        <v>31021296</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>55</v>
       </c>
       <c r="F46" s="19">
-        <v>582</v>
+        <v>323</v>
       </c>
       <c r="G46" s="16">
-        <f t="shared" si="0"/>
-        <v>582</v>
+        <f>ROUND(F46,2)</f>
+        <v>323</v>
       </c>
       <c r="H46" s="8">
         <v>6</v>
@@ -2442,29 +8485,33 @@
         <v>4</v>
       </c>
       <c r="K46" s="1"/>
+      <c r="M46">
+        <f>_xlfn.XLOOKUP(E46,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>323</v>
+      </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D47" s="7">
-        <v>31021296</v>
+        <v>31021299</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>56</v>
       </c>
       <c r="F47" s="19">
-        <v>323</v>
+        <v>407</v>
       </c>
       <c r="G47" s="16">
-        <f t="shared" si="0"/>
-        <v>323</v>
+        <f>ROUND(F47,2)</f>
+        <v>407</v>
       </c>
       <c r="H47" s="8">
         <v>6</v>
@@ -2473,29 +8520,33 @@
         <v>4</v>
       </c>
       <c r="K47" s="1"/>
+      <c r="M47">
+        <f>_xlfn.XLOOKUP(E47,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>407</v>
+      </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D48" s="7">
-        <v>31021299</v>
+        <v>31103164</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>57</v>
       </c>
       <c r="F48" s="19">
-        <v>407</v>
+        <v>329</v>
       </c>
       <c r="G48" s="16">
-        <f t="shared" si="0"/>
-        <v>407</v>
+        <f>ROUND(F48,2)</f>
+        <v>329</v>
       </c>
       <c r="H48" s="8">
         <v>6</v>
@@ -2504,29 +8555,33 @@
         <v>4</v>
       </c>
       <c r="K48" s="1"/>
+      <c r="M48">
+        <f>_xlfn.XLOOKUP(E48,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>329</v>
+      </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D49" s="7">
-        <v>31103164</v>
+        <v>31103162</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>58</v>
       </c>
       <c r="F49" s="19">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="G49" s="16">
-        <f t="shared" si="0"/>
-        <v>329</v>
+        <f>ROUND(F49,2)</f>
+        <v>335</v>
       </c>
       <c r="H49" s="8">
         <v>6</v>
@@ -2535,29 +8590,33 @@
         <v>4</v>
       </c>
       <c r="K49" s="1"/>
+      <c r="M49">
+        <f>_xlfn.XLOOKUP(E49,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>335</v>
+      </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D50" s="7">
-        <v>31103162</v>
+        <v>31103166</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>59</v>
       </c>
       <c r="F50" s="19">
-        <v>335</v>
+        <v>428</v>
       </c>
       <c r="G50" s="16">
-        <f t="shared" si="0"/>
-        <v>335</v>
+        <f>ROUND(F50,2)</f>
+        <v>428</v>
       </c>
       <c r="H50" s="8">
         <v>6</v>
@@ -2566,29 +8625,33 @@
         <v>4</v>
       </c>
       <c r="K50" s="1"/>
+      <c r="M50">
+        <f>_xlfn.XLOOKUP(E50,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>428</v>
+      </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D51" s="7">
-        <v>31103166</v>
+        <v>31103163</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>60</v>
       </c>
       <c r="F51" s="19">
-        <v>428</v>
+        <v>472</v>
       </c>
       <c r="G51" s="16">
-        <f t="shared" si="0"/>
-        <v>428</v>
+        <f>ROUND(F51,2)</f>
+        <v>472</v>
       </c>
       <c r="H51" s="8">
         <v>6</v>
@@ -2597,91 +8660,103 @@
         <v>4</v>
       </c>
       <c r="K51" s="1"/>
+      <c r="M51">
+        <f>_xlfn.XLOOKUP(E51,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>472</v>
+      </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>91</v>
+        <v>3</v>
+      </c>
+      <c r="C52" s="7">
+        <v>8888</v>
       </c>
       <c r="D52" s="7">
-        <v>31103163</v>
+        <v>31021468</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>61</v>
       </c>
       <c r="F52" s="19">
-        <v>472</v>
+        <v>646</v>
       </c>
       <c r="G52" s="16">
-        <f t="shared" si="0"/>
-        <v>472</v>
-      </c>
-      <c r="H52" s="8">
-        <v>6</v>
+        <f>ROUND(F52,2)</f>
+        <v>646</v>
+      </c>
+      <c r="H52" s="7">
+        <v>12</v>
       </c>
       <c r="I52" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K52" s="1"/>
+      <c r="M52">
+        <f>_xlfn.XLOOKUP(E52,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>646</v>
+      </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="7">
-        <v>8888</v>
+      <c r="C53" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="D53" s="7">
-        <v>31021468</v>
+        <v>31020590</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>62</v>
       </c>
       <c r="F53" s="19">
-        <v>646</v>
+        <v>379</v>
       </c>
       <c r="G53" s="16">
-        <f t="shared" si="0"/>
-        <v>646</v>
+        <f>ROUND(F53,2)</f>
+        <v>379</v>
       </c>
       <c r="H53" s="7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I53" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K53" s="1"/>
+      <c r="M53">
+        <f>_xlfn.XLOOKUP(E53,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>379</v>
+      </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D54" s="7">
-        <v>31020590</v>
+        <v>31021015</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>63</v>
       </c>
       <c r="F54" s="19">
-        <v>379</v>
+        <v>499</v>
       </c>
       <c r="G54" s="16">
-        <f t="shared" si="0"/>
-        <v>379</v>
+        <f>ROUND(F54,2)</f>
+        <v>499</v>
       </c>
       <c r="H54" s="7">
         <v>6</v>
@@ -2690,29 +8765,33 @@
         <v>4</v>
       </c>
       <c r="K54" s="1"/>
+      <c r="M54">
+        <f>_xlfn.XLOOKUP(E54,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>499</v>
+      </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D55" s="7">
-        <v>31021015</v>
+        <v>31020436</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>64</v>
       </c>
       <c r="F55" s="19">
-        <v>499</v>
+        <v>299</v>
       </c>
       <c r="G55" s="16">
-        <f t="shared" si="0"/>
-        <v>499</v>
+        <f>ROUND(F55,2)</f>
+        <v>299</v>
       </c>
       <c r="H55" s="7">
         <v>6</v>
@@ -2721,225 +8800,298 @@
         <v>4</v>
       </c>
       <c r="K55" s="1"/>
+      <c r="M55">
+        <f>_xlfn.XLOOKUP(E55,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>299</v>
+      </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>91</v>
+        <v>77</v>
+      </c>
+      <c r="C56" s="7">
+        <v>9999</v>
       </c>
       <c r="D56" s="7">
-        <v>31020436</v>
+        <v>31020735</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>65</v>
       </c>
       <c r="F56" s="19">
-        <v>299</v>
+        <v>583</v>
       </c>
       <c r="G56" s="16">
-        <f t="shared" si="0"/>
-        <v>299</v>
+        <f>ROUND(F56,2)</f>
+        <v>583</v>
       </c>
       <c r="H56" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I56" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K56" s="1"/>
+      <c r="M56">
+        <f>_xlfn.XLOOKUP(E56,[1]Washing!$E:$E,[1]Washing!$DM:$DM)</f>
+        <v>583</v>
+      </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C57" s="7">
-        <v>9999</v>
-      </c>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D57" s="7">
-        <v>31020735</v>
+        <v>31020140</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F57" s="19">
-        <v>583</v>
-      </c>
-      <c r="G57" s="16">
-        <f t="shared" si="0"/>
-        <v>583</v>
-      </c>
-      <c r="H57" s="7">
-        <v>12</v>
-      </c>
-      <c r="I57" s="12">
-        <v>2</v>
-      </c>
-      <c r="K57" s="1"/>
+        <v>100</v>
+      </c>
     </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D58" s="7">
+        <v>31020591</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D59" s="7">
+        <v>31102816</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62"/>
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63"/>
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="H63"/>
+      <c r="I63"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64"/>
+      <c r="B64"/>
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64"/>
+      <c r="I64"/>
+    </row>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:L57" xr:uid="{4D870034-242D-49C0-BE89-40E84D61E957}"/>
+  <autoFilter ref="A1:L59" xr:uid="{4D870034-242D-49C0-BE89-40E84D61E957}"/>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF Haier Europe - Internal and trusted parties</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5976AE87-395E-43D1-BB7D-A2A12FDB9EFF}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" customWidth="1"/>
     <col min="2" max="7" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>67</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
         <v>91</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E7" t="s">
         <v>91</v>
       </c>
-      <c r="D2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" t="s">
-        <v>91</v>
+      <c r="F7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" t="s">
-        <v>93</v>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" t="s">
-        <v>93</v>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" t="s">
-        <v>93</v>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" t="s">
-        <v>93</v>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>88</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
@@ -2951,12 +9103,12 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -2974,11 +9126,14 @@
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K0000FF Haier Europe - Internal and trusted parties</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{41b89379-e28c-4971-b9ce-0b428bf8dafd}" enabled="0" method="" siteId="{41b89379-e28c-4971-b9ce-0b428bf8dafd}" removed="1"/>
+  <clbl:label id="{dc31490c-19d9-4676-a99d-07ae2489f322}" enabled="1" method="Standard" siteId="{41b89379-e28c-4971-b9ce-0b428bf8dafd}" contentBits="2" removed="0"/>
 </clbl:labelList>
 </file>